--- a/nemuranai/production/製作費見積もり_第320稿.xlsx
+++ b/nemuranai/production/製作費見積もり_第320稿.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="香盤" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積もり" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="根拠" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="撮影スケジュールA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スタッフ機材A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="香盤" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積もり" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="根拠" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +59,13 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +125,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -799,6 +816,937 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>ミニマム（ホン・サンス型）撮影スケジュール案　順撮り・13撮影日＋休み3日＝16日間</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>物語の順に撮る（倉田の疲れが画に溜まっていく）。夜と夜明けが続くので、3〜4日ごとに休みを入れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>撮る場</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>時間帯</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>撮影日数</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>出演</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ねらい・注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1日目</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>L1 布団屋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>昼</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>倉田・アベ・店長・客の男</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>実演のマットレスで倉田が本当に眠る。商店街の許可</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2日目</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>L2 アパート204号室</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>夜〜朝</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>九平米。看板の照り返しだけで撮る</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>3日目</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>3・4</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>L2 アパート前→204号室</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>夜→朝</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3場は植え込みの陰から一カット。そのまま朝の4場へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr"/>
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr"/>
+      <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>4日目</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>L3 雑居ビル（エレベーター・白い部屋）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁・アベ・受講生</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4:3からスコープへの切り替えは編集で</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5日目</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>6・7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>L3 給湯室・白い部屋</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁・アベ</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7場は給湯室の一カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6日目</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>L3 給湯室の奥</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>昼〜夕</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・アベ・コールセンターの女</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>唯一の昼の雑居ビル。体を休める日にもなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr"/>
+      <c r="C12" s="22" t="inlineStr"/>
+      <c r="D12" s="22" t="inlineStr"/>
+      <c r="E12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>7日目</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>L3 白い部屋</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>夜〜未明</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁・アベ・コールセンターの女</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>8日目</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>L4 非常階段・九階の踊り場</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>夜明け</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>夜明けは約20分で1テイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9日目</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>L4 非常階段〜駐車場</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>夜明け</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>約10分の一カット（1回目）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10日目</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>L4 非常階段〜駐車場</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>夜明け</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>同（予備・2回目）。良ければ11日目を前倒し</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr"/>
+      <c r="C17" s="22" t="inlineStr"/>
+      <c r="D17" s="22" t="inlineStr"/>
+      <c r="E17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>11日目</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>L5 団地</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>昼</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・アベ・男の子</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>子役は昼のみ、21時まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>12日目</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>L3 白い部屋</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>夜〜夜明け</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁・受講生</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>真壁の語り〜入眠の一カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>13日目</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>L3 白い部屋</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>夜明け〜朝</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>倉田・ミオ・真壁</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>結末の一カット（ミオが起きる〜4:3に閉じる）。残り半日は予備</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>撮影日数の合計</t>
+        </is>
+      </c>
+      <c r="E21" s="7">
+        <f>SUM(E5:E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>香盤シートのAの合計</t>
+        </is>
+      </c>
+      <c r="E22" s="24">
+        <f>香盤!K17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>L3（白い部屋・給湯室）は4〜7日目と12〜13日目の2回に分かれる。1か月借りれば続けて押さえられる（見積もりの前提）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>L3とL4が同じビルなら、8〜10日目も同じ物件で済む。物件探しの第一条件にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>俳優を本当に寝不足にして撮ることはしない。疲れは撮る順番と休みの置き方で作る。俳優の健康と安全、労働時間の問題になるため（確信度 高）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>ミニマム（ホン・サンス型）スタッフと機材</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>監督・脚本</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>早坂</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>現場で台詞を直す。撮影当日の朝に、その日の場を読み直す時間を取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>撮影（照明を兼ねる）</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ズームで寄る。画に映る明かり（看板・蛍光灯・誘導灯）を主にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>撮影助手</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ピント・記録媒体・機材の管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>録音</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ガンマイク＋ピンマイク。会話劇なので一番削れない所</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>助監督・制作進行</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>スケジュール・許可・食事・移動を一人で回す</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>美術・衣装・メイク</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>白い部屋の塗り、小道具、衣装、メイクを兼ねる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>ホン・サンスの組み方に近い最小の人数（確信度 中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>機材</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>カメラ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sony FX6級＋ズームレンズ1本＋単焦点1本</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FX6本体は1日約8,500〜22,000円（確信度 高）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>三脚</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>重めのビデオ三脚1台</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>固定の長回しが多い。台本の「長いレンズで、動かない」に合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>照明</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>小型LED 2〜3灯、電球、延長コード</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>主役は現場の明かり。白い部屋の蛍光灯は美術で作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>録音</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ガンマイク、ピンマイク2本、録音機</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>長回しでも台詞を落とさない</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>記録・編集</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>記録媒体、ハードディスク、自社の編集機</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>編集は自社（見積もりAの前提）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>車両</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>機材車1台（レンタル）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>L3とL4が同じビルなら移動が減る</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1687,7 +2635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4003,7 +4951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
